--- a/data/ab_test_voting_results.xlsx
+++ b/data/ab_test_voting_results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="34">
   <si>
     <t xml:space="preserve">pair_id</t>
   </si>
@@ -118,6 +118,12 @@
   <si>
     <t xml:space="preserve">Was sind aktuelle Ansätze für intelligente Umgebungswahrnehmung beim Autonomen Fahren?</t>
   </si>
+  <si>
+    <t xml:space="preserve">Wie unterscheidet sich die zustandsorientierte Instandhaltung (CBM) von herkömmlichen Methoden?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gleichwertig</t>
+  </si>
 </sst>
 </file>
 
@@ -212,28 +218,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,4409 +500,4426 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1048576"/>
+  <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="5" style="0" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="13.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="5" style="1" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>173</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E59" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
+    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D60" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E60" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
+    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C61" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E61" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
+    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C62" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D62" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E62" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="4"/>
-    </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="4"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="4"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="4"/>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="4"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="4"/>
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="4"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="4"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="4"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="4"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="4"/>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="4"/>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="4"/>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="4"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="4"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="4"/>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="4"/>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="4"/>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="4"/>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="4"/>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="4"/>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="4"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="4"/>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="4"/>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="4"/>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="4"/>
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="4"/>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="4"/>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="4"/>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="4"/>
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="4"/>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="4"/>
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="4"/>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="4"/>
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="4"/>
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="4"/>
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="4"/>
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="4"/>
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="5"/>
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="5"/>
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="7"/>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="5"/>
+      <c r="A102" s="2"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="7"/>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="5"/>
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="7"/>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="5"/>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="7"/>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="5"/>
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="5"/>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="7"/>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="5"/>
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="7"/>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="5"/>
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="5"/>
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="7"/>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="5"/>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="5"/>
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="7"/>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="5"/>
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="7"/>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="5"/>
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="7"/>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="5"/>
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="7"/>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="5"/>
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="7"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="5"/>
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="7"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="5"/>
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="7"/>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="5"/>
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="7"/>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="5"/>
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="7"/>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="5"/>
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="7"/>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="5"/>
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="7"/>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="5"/>
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="7"/>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="5"/>
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="7"/>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="5"/>
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="7"/>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="5"/>
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="7"/>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="5"/>
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="7"/>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="5"/>
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="7"/>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="5"/>
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="7"/>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="5"/>
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="7"/>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="5"/>
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="7"/>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="5"/>
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="7"/>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="5"/>
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="7"/>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="5"/>
+      <c r="A133" s="2"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="7"/>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="5"/>
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="7"/>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="5"/>
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="7"/>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="5"/>
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="7"/>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="5"/>
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="7"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
-      <c r="E138" s="5"/>
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="7"/>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-      <c r="E139" s="5"/>
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="7"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="5"/>
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="7"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="E141" s="5"/>
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="7"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-      <c r="E142" s="5"/>
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="7"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-      <c r="E143" s="5"/>
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="7"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-      <c r="E144" s="5"/>
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="7"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
-      <c r="E145" s="5"/>
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="7"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
-      <c r="E146" s="5"/>
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="7"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
-      <c r="E147" s="5"/>
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="7"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
-      <c r="E148" s="5"/>
+      <c r="A148" s="2"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="7"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="5"/>
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="7"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
-      <c r="E150" s="5"/>
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="7"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
-      <c r="E151" s="5"/>
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="7"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
-      <c r="E152" s="5"/>
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="7"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1"/>
-      <c r="B153" s="3"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="5"/>
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="7"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
-      <c r="E154" s="5"/>
+      <c r="A154" s="2"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="7"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
-      <c r="E155" s="5"/>
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="7"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
-      <c r="E156" s="5"/>
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="7"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1"/>
-      <c r="B157" s="3"/>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
-      <c r="E157" s="5"/>
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="7"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
-      <c r="E158" s="5"/>
+      <c r="A158" s="2"/>
+      <c r="B158" s="4"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="7"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="5"/>
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="7"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1"/>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-      <c r="E160" s="5"/>
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="7"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
-      <c r="E161" s="5"/>
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="7"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1"/>
-      <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
-      <c r="E162" s="5"/>
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="7"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1"/>
-      <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
-      <c r="E163" s="5"/>
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="7"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-      <c r="E164" s="5"/>
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="7"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1"/>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-      <c r="E165" s="5"/>
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="7"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1"/>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
-      <c r="E166" s="5"/>
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="7"/>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1"/>
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
-      <c r="E167" s="5"/>
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="7"/>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1"/>
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
-      <c r="E168" s="5"/>
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="7"/>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="E169" s="5"/>
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="7"/>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="1"/>
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
-      <c r="E170" s="5"/>
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="7"/>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1"/>
-      <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
-      <c r="E171" s="5"/>
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="7"/>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1"/>
-      <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
-      <c r="E172" s="5"/>
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="7"/>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
-      <c r="E173" s="5"/>
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="7"/>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
-      <c r="E174" s="5"/>
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="7"/>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
-      <c r="E175" s="5"/>
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="7"/>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
-      <c r="E176" s="5"/>
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="7"/>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
-      <c r="E177" s="5"/>
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="7"/>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="E178" s="5"/>
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="7"/>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="5"/>
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="7"/>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-      <c r="E180" s="5"/>
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="7"/>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
-      <c r="E181" s="5"/>
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="7"/>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
-      <c r="E182" s="5"/>
+      <c r="A182" s="2"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="7"/>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
-      <c r="E183" s="5"/>
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="7"/>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
-      <c r="E184" s="5"/>
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="7"/>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="1"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
-      <c r="E185" s="5"/>
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="7"/>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
-      <c r="E186" s="5"/>
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="7"/>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
-      <c r="E187" s="5"/>
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="7"/>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
-      <c r="E188" s="5"/>
+      <c r="A188" s="2"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="7"/>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1"/>
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
-      <c r="E189" s="5"/>
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="5"/>
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="7"/>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
-      <c r="E191" s="5"/>
+      <c r="A191" s="2"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="7"/>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="5"/>
+      <c r="A192" s="2"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="7"/>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
-      <c r="E193" s="5"/>
+      <c r="A193" s="2"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="7"/>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
-      <c r="E194" s="5"/>
+      <c r="A194" s="2"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="7"/>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1"/>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
-      <c r="E195" s="5"/>
+      <c r="A195" s="2"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="7"/>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1"/>
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
-      <c r="E196" s="5"/>
+      <c r="A196" s="2"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="7"/>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E197" s="5"/>
+      <c r="A197" s="2"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="7"/>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E198" s="5"/>
+      <c r="E198" s="7"/>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E199" s="5"/>
+      <c r="E199" s="7"/>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E200" s="5"/>
+      <c r="E200" s="7"/>
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E201" s="5"/>
+      <c r="E201" s="7"/>
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E202" s="5"/>
+      <c r="E202" s="7"/>
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E203" s="5"/>
+      <c r="E203" s="7"/>
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E204" s="5"/>
+      <c r="E204" s="7"/>
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E205" s="5"/>
+      <c r="E205" s="7"/>
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E206" s="5"/>
+      <c r="E206" s="7"/>
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E207" s="5"/>
+      <c r="E207" s="7"/>
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E208" s="5"/>
+      <c r="E208" s="7"/>
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E209" s="5"/>
+      <c r="E209" s="7"/>
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E210" s="5"/>
+      <c r="E210" s="7"/>
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E211" s="5"/>
+      <c r="E211" s="7"/>
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E212" s="5"/>
+      <c r="E212" s="7"/>
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E213" s="5"/>
+      <c r="E213" s="7"/>
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E214" s="5"/>
+      <c r="E214" s="7"/>
     </row>
     <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E215" s="5"/>
+      <c r="E215" s="7"/>
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E216" s="5"/>
+      <c r="E216" s="7"/>
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E217" s="5"/>
+      <c r="E217" s="7"/>
     </row>
     <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E218" s="5"/>
+      <c r="E218" s="7"/>
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E219" s="5"/>
+      <c r="E219" s="7"/>
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E220" s="5"/>
+      <c r="E220" s="7"/>
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E221" s="5"/>
+      <c r="E221" s="7"/>
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E222" s="5"/>
+      <c r="E222" s="7"/>
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E223" s="5"/>
+      <c r="E223" s="7"/>
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E224" s="5"/>
+      <c r="E224" s="7"/>
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E225" s="5"/>
+      <c r="E225" s="7"/>
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E226" s="5"/>
+      <c r="E226" s="7"/>
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E227" s="5"/>
+      <c r="E227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E228" s="5"/>
+      <c r="E228" s="7"/>
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E229" s="5"/>
+      <c r="E229" s="7"/>
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E230" s="5"/>
+      <c r="E230" s="7"/>
     </row>
     <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E231" s="5"/>
+      <c r="E231" s="7"/>
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E232" s="5"/>
+      <c r="E232" s="7"/>
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E233" s="5"/>
+      <c r="E233" s="7"/>
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E234" s="5"/>
+      <c r="E234" s="7"/>
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E235" s="5"/>
+      <c r="E235" s="7"/>
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E236" s="5"/>
+      <c r="E236" s="7"/>
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E237" s="5"/>
+      <c r="E237" s="7"/>
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E238" s="5"/>
+      <c r="E238" s="7"/>
     </row>
     <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E239" s="5"/>
+      <c r="E239" s="7"/>
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E240" s="5"/>
+      <c r="E240" s="7"/>
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E241" s="5"/>
+      <c r="E241" s="7"/>
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E242" s="5"/>
+      <c r="E242" s="7"/>
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E243" s="5"/>
+      <c r="E243" s="7"/>
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E244" s="5"/>
+      <c r="E244" s="7"/>
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E245" s="5"/>
+      <c r="E245" s="7"/>
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E246" s="5"/>
+      <c r="E246" s="7"/>
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E247" s="5"/>
+      <c r="E247" s="7"/>
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E248" s="5"/>
+      <c r="E248" s="7"/>
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E249" s="5"/>
+      <c r="E249" s="7"/>
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E250" s="5"/>
+      <c r="E250" s="7"/>
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E251" s="5"/>
+      <c r="E251" s="7"/>
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E252" s="5"/>
+      <c r="E252" s="7"/>
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E253" s="5"/>
+      <c r="E253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E254" s="5"/>
+      <c r="E254" s="7"/>
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E255" s="5"/>
+      <c r="E255" s="7"/>
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E256" s="5"/>
+      <c r="E256" s="7"/>
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E257" s="5"/>
+      <c r="E257" s="7"/>
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E258" s="5"/>
+      <c r="E258" s="7"/>
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E259" s="5"/>
+      <c r="E259" s="7"/>
     </row>
     <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E260" s="5"/>
+      <c r="E260" s="7"/>
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E261" s="5"/>
+      <c r="E261" s="7"/>
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E262" s="5"/>
+      <c r="E262" s="7"/>
     </row>
     <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E263" s="5"/>
+      <c r="E263" s="7"/>
     </row>
     <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E264" s="5"/>
+      <c r="E264" s="7"/>
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E265" s="5"/>
+      <c r="E265" s="7"/>
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E266" s="5"/>
+      <c r="E266" s="7"/>
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E267" s="5"/>
+      <c r="E267" s="7"/>
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E268" s="5"/>
+      <c r="E268" s="7"/>
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E269" s="5"/>
+      <c r="E269" s="7"/>
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E270" s="5"/>
+      <c r="E270" s="7"/>
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E271" s="5"/>
+      <c r="E271" s="7"/>
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E272" s="5"/>
+      <c r="E272" s="7"/>
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E273" s="5"/>
+      <c r="E273" s="7"/>
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E274" s="5"/>
+      <c r="E274" s="7"/>
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E275" s="5"/>
+      <c r="E275" s="7"/>
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E276" s="5"/>
+      <c r="E276" s="7"/>
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E277" s="5"/>
+      <c r="E277" s="7"/>
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E278" s="5"/>
+      <c r="E278" s="7"/>
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E279" s="5"/>
+      <c r="E279" s="7"/>
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E280" s="5"/>
+      <c r="E280" s="7"/>
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E281" s="5"/>
+      <c r="E281" s="7"/>
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E282" s="5"/>
+      <c r="E282" s="7"/>
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E283" s="5"/>
+      <c r="E283" s="7"/>
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E284" s="5"/>
+      <c r="E284" s="7"/>
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E285" s="5"/>
+      <c r="E285" s="7"/>
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E286" s="5"/>
+      <c r="E286" s="7"/>
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E287" s="5"/>
+      <c r="E287" s="7"/>
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E288" s="5"/>
+      <c r="E288" s="7"/>
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E289" s="5"/>
+      <c r="E289" s="7"/>
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E290" s="5"/>
+      <c r="E290" s="7"/>
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E291" s="5"/>
+      <c r="E291" s="7"/>
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E292" s="5"/>
+      <c r="E292" s="7"/>
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E293" s="5"/>
+      <c r="E293" s="7"/>
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E294" s="5"/>
+      <c r="E294" s="7"/>
     </row>
     <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E295" s="5"/>
+      <c r="E295" s="7"/>
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E296" s="5"/>
+      <c r="E296" s="7"/>
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E297" s="5"/>
+      <c r="E297" s="7"/>
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E298" s="5"/>
+      <c r="E298" s="7"/>
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E299" s="5"/>
+      <c r="E299" s="7"/>
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E300" s="5"/>
+      <c r="E300" s="7"/>
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E301" s="5"/>
+      <c r="E301" s="7"/>
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E302" s="5"/>
+      <c r="E302" s="7"/>
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E303" s="5"/>
+      <c r="E303" s="7"/>
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E304" s="5"/>
+      <c r="E304" s="7"/>
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E305" s="5"/>
+      <c r="E305" s="7"/>
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E306" s="5"/>
+      <c r="E306" s="7"/>
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E307" s="5"/>
+      <c r="E307" s="7"/>
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E308" s="5"/>
+      <c r="E308" s="7"/>
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E309" s="5"/>
+      <c r="E309" s="7"/>
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E310" s="5"/>
+      <c r="E310" s="7"/>
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E311" s="5"/>
+      <c r="E311" s="7"/>
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E312" s="5"/>
+      <c r="E312" s="7"/>
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E313" s="5"/>
+      <c r="E313" s="7"/>
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E314" s="5"/>
+      <c r="E314" s="7"/>
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E315" s="5"/>
+      <c r="E315" s="7"/>
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E316" s="5"/>
+      <c r="E316" s="7"/>
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E317" s="5"/>
+      <c r="E317" s="7"/>
     </row>
     <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E318" s="5"/>
+      <c r="E318" s="7"/>
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E319" s="5"/>
+      <c r="E319" s="7"/>
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E320" s="5"/>
+      <c r="E320" s="7"/>
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E321" s="5"/>
+      <c r="E321" s="7"/>
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E322" s="5"/>
+      <c r="E322" s="7"/>
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E323" s="5"/>
+      <c r="E323" s="7"/>
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E324" s="5"/>
+      <c r="E324" s="7"/>
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E325" s="5"/>
+      <c r="E325" s="7"/>
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E326" s="5"/>
+      <c r="E326" s="7"/>
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E327" s="5"/>
+      <c r="E327" s="7"/>
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E328" s="5"/>
+      <c r="E328" s="7"/>
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E329" s="5"/>
+      <c r="E329" s="7"/>
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E330" s="5"/>
+      <c r="E330" s="7"/>
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E331" s="5"/>
+      <c r="E331" s="7"/>
     </row>
     <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E332" s="5"/>
+      <c r="E332" s="7"/>
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E333" s="5"/>
+      <c r="E333" s="7"/>
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E334" s="5"/>
+      <c r="E334" s="7"/>
     </row>
     <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E335" s="5"/>
+      <c r="E335" s="7"/>
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E336" s="5"/>
+      <c r="E336" s="7"/>
     </row>
     <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E337" s="5"/>
+      <c r="E337" s="7"/>
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E338" s="5"/>
+      <c r="E338" s="7"/>
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E339" s="5"/>
+      <c r="E339" s="7"/>
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E340" s="5"/>
+      <c r="E340" s="7"/>
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E341" s="5"/>
+      <c r="E341" s="7"/>
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E342" s="5"/>
+      <c r="E342" s="7"/>
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E343" s="5"/>
+      <c r="E343" s="7"/>
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E344" s="5"/>
+      <c r="E344" s="7"/>
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E345" s="5"/>
+      <c r="E345" s="7"/>
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E346" s="5"/>
+      <c r="E346" s="7"/>
     </row>
     <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E347" s="5"/>
+      <c r="E347" s="7"/>
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E348" s="5"/>
+      <c r="E348" s="7"/>
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E349" s="5"/>
+      <c r="E349" s="7"/>
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E350" s="5"/>
+      <c r="E350" s="7"/>
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E351" s="5"/>
+      <c r="E351" s="7"/>
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E352" s="5"/>
+      <c r="E352" s="7"/>
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E353" s="5"/>
+      <c r="E353" s="7"/>
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E354" s="5"/>
+      <c r="E354" s="7"/>
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E355" s="5"/>
+      <c r="E355" s="7"/>
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E356" s="5"/>
+      <c r="E356" s="7"/>
     </row>
     <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E357" s="5"/>
+      <c r="E357" s="7"/>
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E358" s="5"/>
+      <c r="E358" s="7"/>
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E359" s="5"/>
+      <c r="E359" s="7"/>
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E360" s="5"/>
+      <c r="E360" s="7"/>
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E361" s="5"/>
+      <c r="E361" s="7"/>
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E362" s="5"/>
+      <c r="E362" s="7"/>
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E363" s="5"/>
+      <c r="E363" s="7"/>
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E364" s="5"/>
+      <c r="E364" s="7"/>
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E365" s="5"/>
+      <c r="E365" s="7"/>
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E366" s="5"/>
+      <c r="E366" s="7"/>
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E367" s="5"/>
+      <c r="E367" s="7"/>
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E368" s="5"/>
+      <c r="E368" s="7"/>
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E369" s="5"/>
+      <c r="E369" s="7"/>
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E370" s="5"/>
+      <c r="E370" s="7"/>
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E371" s="5"/>
+      <c r="E371" s="7"/>
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E372" s="5"/>
+      <c r="E372" s="7"/>
     </row>
     <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E373" s="5"/>
+      <c r="E373" s="7"/>
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E374" s="5"/>
+      <c r="E374" s="7"/>
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E375" s="5"/>
+      <c r="E375" s="7"/>
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E376" s="5"/>
+      <c r="E376" s="7"/>
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E377" s="5"/>
+      <c r="E377" s="7"/>
     </row>
     <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E378" s="5"/>
+      <c r="E378" s="7"/>
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E379" s="5"/>
+      <c r="E379" s="7"/>
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E380" s="5"/>
+      <c r="E380" s="7"/>
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E381" s="5"/>
+      <c r="E381" s="7"/>
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E382" s="5"/>
+      <c r="E382" s="7"/>
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E383" s="5"/>
+      <c r="E383" s="7"/>
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E384" s="5"/>
+      <c r="E384" s="7"/>
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E385" s="5"/>
+      <c r="E385" s="7"/>
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E386" s="5"/>
+      <c r="E386" s="7"/>
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E387" s="5"/>
+      <c r="E387" s="7"/>
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E388" s="5"/>
+      <c r="E388" s="7"/>
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E389" s="5"/>
+      <c r="E389" s="7"/>
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E390" s="5"/>
+      <c r="E390" s="7"/>
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E391" s="5"/>
+      <c r="E391" s="7"/>
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E392" s="5"/>
+      <c r="E392" s="7"/>
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E393" s="5"/>
+      <c r="E393" s="7"/>
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E394" s="5"/>
+      <c r="E394" s="7"/>
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E395" s="5"/>
+      <c r="E395" s="7"/>
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E396" s="5"/>
+      <c r="E396" s="7"/>
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E397" s="5"/>
+      <c r="E397" s="7"/>
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E398" s="5"/>
+      <c r="E398" s="7"/>
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E399" s="5"/>
+      <c r="E399" s="7"/>
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E400" s="5"/>
+      <c r="E400" s="7"/>
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E401" s="5"/>
+      <c r="E401" s="7"/>
     </row>
     <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E402" s="5"/>
+      <c r="E402" s="7"/>
     </row>
     <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E403" s="5"/>
+      <c r="E403" s="7"/>
     </row>
     <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E404" s="5"/>
+      <c r="E404" s="7"/>
     </row>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E405" s="5"/>
+      <c r="E405" s="7"/>
     </row>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E406" s="5"/>
+      <c r="E406" s="7"/>
     </row>
     <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E407" s="5"/>
+      <c r="E407" s="7"/>
     </row>
     <row r="408" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E408" s="5"/>
+      <c r="E408" s="7"/>
     </row>
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E409" s="5"/>
+      <c r="E409" s="7"/>
     </row>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E410" s="5"/>
+      <c r="E410" s="7"/>
     </row>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E411" s="5"/>
+      <c r="E411" s="7"/>
     </row>
     <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E412" s="5"/>
+      <c r="E412" s="7"/>
     </row>
     <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E413" s="5"/>
+      <c r="E413" s="7"/>
     </row>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E414" s="5"/>
+      <c r="E414" s="7"/>
     </row>
     <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E415" s="5"/>
+      <c r="E415" s="7"/>
     </row>
     <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E416" s="5"/>
+      <c r="E416" s="7"/>
     </row>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E417" s="5"/>
+      <c r="E417" s="7"/>
     </row>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E418" s="5"/>
+      <c r="E418" s="7"/>
     </row>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E419" s="5"/>
+      <c r="E419" s="7"/>
     </row>
     <row r="420" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E420" s="5"/>
+      <c r="E420" s="7"/>
     </row>
     <row r="421" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E421" s="5"/>
+      <c r="E421" s="7"/>
     </row>
     <row r="422" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E422" s="5"/>
+      <c r="E422" s="7"/>
     </row>
     <row r="423" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E423" s="5"/>
+      <c r="E423" s="7"/>
     </row>
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E424" s="5"/>
+      <c r="E424" s="7"/>
     </row>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E425" s="5"/>
+      <c r="E425" s="7"/>
     </row>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E426" s="5"/>
+      <c r="E426" s="7"/>
     </row>
     <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E427" s="5"/>
+      <c r="E427" s="7"/>
     </row>
     <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E428" s="5"/>
+      <c r="E428" s="7"/>
     </row>
     <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E429" s="5"/>
+      <c r="E429" s="7"/>
     </row>
     <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E430" s="5"/>
+      <c r="E430" s="7"/>
     </row>
     <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E431" s="5"/>
+      <c r="E431" s="7"/>
     </row>
     <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E432" s="5"/>
+      <c r="E432" s="7"/>
     </row>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E433" s="5"/>
+      <c r="E433" s="7"/>
     </row>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E434" s="5"/>
+      <c r="E434" s="7"/>
     </row>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E435" s="5"/>
+      <c r="E435" s="7"/>
     </row>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E436" s="5"/>
+      <c r="E436" s="7"/>
     </row>
     <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E437" s="5"/>
+      <c r="E437" s="7"/>
     </row>
     <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E438" s="5"/>
+      <c r="E438" s="7"/>
     </row>
     <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E439" s="5"/>
+      <c r="E439" s="7"/>
     </row>
     <row r="440" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E440" s="5"/>
+      <c r="E440" s="7"/>
     </row>
     <row r="441" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E441" s="5"/>
+      <c r="E441" s="7"/>
     </row>
     <row r="442" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E442" s="5"/>
+      <c r="E442" s="7"/>
     </row>
     <row r="443" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E443" s="5"/>
+      <c r="E443" s="7"/>
     </row>
     <row r="444" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E444" s="5"/>
+      <c r="E444" s="7"/>
     </row>
     <row r="445" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E445" s="5"/>
+      <c r="E445" s="7"/>
     </row>
     <row r="446" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E446" s="5"/>
+      <c r="E446" s="7"/>
     </row>
     <row r="447" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E447" s="5"/>
+      <c r="E447" s="7"/>
     </row>
     <row r="448" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E448" s="5"/>
+      <c r="E448" s="7"/>
     </row>
     <row r="449" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E449" s="5"/>
+      <c r="E449" s="7"/>
     </row>
     <row r="450" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E450" s="5"/>
+      <c r="E450" s="7"/>
     </row>
     <row r="451" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E451" s="5"/>
+      <c r="E451" s="7"/>
     </row>
     <row r="452" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E452" s="5"/>
+      <c r="E452" s="7"/>
     </row>
     <row r="453" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E453" s="5"/>
+      <c r="E453" s="7"/>
     </row>
     <row r="454" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E454" s="5"/>
+      <c r="E454" s="7"/>
     </row>
     <row r="455" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E455" s="5"/>
+      <c r="E455" s="7"/>
     </row>
     <row r="456" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E456" s="5"/>
+      <c r="E456" s="7"/>
     </row>
     <row r="457" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E457" s="5"/>
+      <c r="E457" s="7"/>
     </row>
     <row r="458" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E458" s="5"/>
+      <c r="E458" s="7"/>
     </row>
     <row r="459" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E459" s="5"/>
+      <c r="E459" s="7"/>
     </row>
     <row r="460" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E460" s="5"/>
+      <c r="E460" s="7"/>
     </row>
     <row r="461" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E461" s="5"/>
+      <c r="E461" s="7"/>
     </row>
     <row r="462" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E462" s="5"/>
+      <c r="E462" s="7"/>
     </row>
     <row r="463" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E463" s="5"/>
+      <c r="E463" s="7"/>
     </row>
     <row r="464" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E464" s="5"/>
+      <c r="E464" s="7"/>
     </row>
     <row r="465" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E465" s="5"/>
+      <c r="E465" s="7"/>
     </row>
     <row r="466" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E466" s="5"/>
+      <c r="E466" s="7"/>
     </row>
     <row r="467" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E467" s="5"/>
+      <c r="E467" s="7"/>
     </row>
     <row r="468" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E468" s="5"/>
+      <c r="E468" s="7"/>
     </row>
     <row r="469" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E469" s="5"/>
+      <c r="E469" s="7"/>
     </row>
     <row r="470" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E470" s="5"/>
+      <c r="E470" s="7"/>
     </row>
     <row r="471" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E471" s="5"/>
+      <c r="E471" s="7"/>
     </row>
     <row r="472" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E472" s="5"/>
+      <c r="E472" s="7"/>
     </row>
     <row r="473" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E473" s="5"/>
+      <c r="E473" s="7"/>
     </row>
     <row r="474" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E474" s="5"/>
+      <c r="E474" s="7"/>
     </row>
     <row r="475" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E475" s="5"/>
+      <c r="E475" s="7"/>
     </row>
     <row r="476" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E476" s="5"/>
+      <c r="E476" s="7"/>
     </row>
     <row r="477" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E477" s="5"/>
+      <c r="E477" s="7"/>
     </row>
     <row r="478" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E478" s="5"/>
+      <c r="E478" s="7"/>
     </row>
     <row r="479" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E479" s="5"/>
+      <c r="E479" s="7"/>
     </row>
     <row r="480" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E480" s="5"/>
+      <c r="E480" s="7"/>
     </row>
     <row r="481" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E481" s="5"/>
+      <c r="E481" s="7"/>
     </row>
     <row r="482" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E482" s="5"/>
+      <c r="E482" s="7"/>
     </row>
     <row r="483" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E483" s="5"/>
+      <c r="E483" s="7"/>
     </row>
     <row r="484" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E484" s="5"/>
+      <c r="E484" s="7"/>
     </row>
     <row r="485" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E485" s="5"/>
+      <c r="E485" s="7"/>
     </row>
     <row r="486" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E486" s="5"/>
+      <c r="E486" s="7"/>
     </row>
     <row r="487" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E487" s="5"/>
+      <c r="E487" s="7"/>
     </row>
     <row r="488" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E488" s="5"/>
+      <c r="E488" s="7"/>
     </row>
     <row r="489" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E489" s="5"/>
+      <c r="E489" s="7"/>
     </row>
     <row r="490" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E490" s="5"/>
+      <c r="E490" s="7"/>
     </row>
     <row r="491" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E491" s="5"/>
+      <c r="E491" s="7"/>
     </row>
     <row r="492" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E492" s="5"/>
+      <c r="E492" s="7"/>
     </row>
     <row r="493" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E493" s="5"/>
+      <c r="E493" s="7"/>
     </row>
     <row r="494" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E494" s="5"/>
+      <c r="E494" s="7"/>
     </row>
     <row r="495" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E495" s="5"/>
+      <c r="E495" s="7"/>
     </row>
     <row r="496" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E496" s="5"/>
+      <c r="E496" s="7"/>
     </row>
     <row r="497" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E497" s="5"/>
+      <c r="E497" s="7"/>
     </row>
     <row r="498" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E498" s="5"/>
+      <c r="E498" s="7"/>
     </row>
     <row r="499" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E499" s="5"/>
+      <c r="E499" s="7"/>
     </row>
     <row r="500" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E500" s="5"/>
+      <c r="E500" s="7"/>
     </row>
     <row r="501" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E501" s="5"/>
+      <c r="E501" s="7"/>
     </row>
     <row r="502" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E502" s="5"/>
+      <c r="E502" s="7"/>
     </row>
     <row r="503" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E503" s="5"/>
+      <c r="E503" s="7"/>
     </row>
     <row r="504" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E504" s="5"/>
+      <c r="E504" s="7"/>
     </row>
     <row r="505" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E505" s="5"/>
+      <c r="E505" s="7"/>
     </row>
     <row r="506" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E506" s="5"/>
+      <c r="E506" s="7"/>
     </row>
     <row r="507" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E507" s="5"/>
+      <c r="E507" s="7"/>
     </row>
     <row r="508" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E508" s="5"/>
+      <c r="E508" s="7"/>
     </row>
     <row r="509" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E509" s="5"/>
+      <c r="E509" s="7"/>
     </row>
     <row r="510" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E510" s="5"/>
+      <c r="E510" s="7"/>
     </row>
     <row r="511" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E511" s="5"/>
+      <c r="E511" s="7"/>
     </row>
     <row r="512" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E512" s="5"/>
+      <c r="E512" s="7"/>
     </row>
     <row r="513" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E513" s="5"/>
+      <c r="E513" s="7"/>
     </row>
     <row r="514" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E514" s="5"/>
+      <c r="E514" s="7"/>
     </row>
     <row r="515" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E515" s="5"/>
+      <c r="E515" s="7"/>
     </row>
     <row r="516" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E516" s="5"/>
+      <c r="E516" s="7"/>
     </row>
     <row r="517" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E517" s="5"/>
+      <c r="E517" s="7"/>
     </row>
     <row r="518" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E518" s="5"/>
+      <c r="E518" s="7"/>
     </row>
     <row r="519" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E519" s="5"/>
+      <c r="E519" s="7"/>
     </row>
     <row r="520" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E520" s="5"/>
+      <c r="E520" s="7"/>
     </row>
     <row r="521" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E521" s="5"/>
+      <c r="E521" s="7"/>
     </row>
     <row r="522" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E522" s="5"/>
+      <c r="E522" s="7"/>
     </row>
     <row r="523" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E523" s="5"/>
+      <c r="E523" s="7"/>
     </row>
     <row r="524" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E524" s="5"/>
+      <c r="E524" s="7"/>
     </row>
     <row r="525" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E525" s="5"/>
+      <c r="E525" s="7"/>
     </row>
     <row r="526" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E526" s="5"/>
+      <c r="E526" s="7"/>
     </row>
     <row r="527" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E527" s="5"/>
+      <c r="E527" s="7"/>
     </row>
     <row r="528" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E528" s="5"/>
+      <c r="E528" s="7"/>
     </row>
     <row r="529" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E529" s="5"/>
+      <c r="E529" s="7"/>
     </row>
     <row r="530" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E530" s="5"/>
+      <c r="E530" s="7"/>
     </row>
     <row r="531" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E531" s="5"/>
+      <c r="E531" s="7"/>
     </row>
     <row r="532" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E532" s="5"/>
+      <c r="E532" s="7"/>
     </row>
     <row r="533" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E533" s="5"/>
+      <c r="E533" s="7"/>
     </row>
     <row r="534" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E534" s="5"/>
+      <c r="E534" s="7"/>
     </row>
     <row r="535" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E535" s="5"/>
+      <c r="E535" s="7"/>
     </row>
     <row r="536" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E536" s="5"/>
+      <c r="E536" s="7"/>
     </row>
     <row r="537" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E537" s="5"/>
+      <c r="E537" s="7"/>
     </row>
     <row r="538" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E538" s="5"/>
+      <c r="E538" s="7"/>
     </row>
     <row r="539" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E539" s="5"/>
+      <c r="E539" s="7"/>
     </row>
     <row r="540" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E540" s="5"/>
+      <c r="E540" s="7"/>
     </row>
     <row r="541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E541" s="5"/>
+      <c r="E541" s="7"/>
     </row>
     <row r="542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E542" s="5"/>
+      <c r="E542" s="7"/>
     </row>
     <row r="543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E543" s="5"/>
+      <c r="E543" s="7"/>
     </row>
     <row r="544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E544" s="5"/>
+      <c r="E544" s="7"/>
     </row>
     <row r="545" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E545" s="5"/>
+      <c r="E545" s="7"/>
     </row>
     <row r="546" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E546" s="5"/>
+      <c r="E546" s="7"/>
     </row>
     <row r="547" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E547" s="5"/>
+      <c r="E547" s="7"/>
     </row>
     <row r="548" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E548" s="5"/>
+      <c r="E548" s="7"/>
     </row>
     <row r="549" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E549" s="5"/>
+      <c r="E549" s="7"/>
     </row>
     <row r="550" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E550" s="5"/>
+      <c r="E550" s="7"/>
     </row>
     <row r="551" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E551" s="5"/>
+      <c r="E551" s="7"/>
     </row>
     <row r="552" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E552" s="5"/>
+      <c r="E552" s="7"/>
     </row>
     <row r="553" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E553" s="5"/>
+      <c r="E553" s="7"/>
     </row>
     <row r="554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E554" s="5"/>
+      <c r="E554" s="7"/>
     </row>
     <row r="555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E555" s="5"/>
+      <c r="E555" s="7"/>
     </row>
     <row r="556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E556" s="5"/>
+      <c r="E556" s="7"/>
     </row>
     <row r="557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E557" s="5"/>
+      <c r="E557" s="7"/>
     </row>
     <row r="558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E558" s="5"/>
+      <c r="E558" s="7"/>
     </row>
     <row r="559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E559" s="5"/>
+      <c r="E559" s="7"/>
     </row>
     <row r="560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E560" s="5"/>
+      <c r="E560" s="7"/>
     </row>
     <row r="561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E561" s="5"/>
+      <c r="E561" s="7"/>
     </row>
     <row r="562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E562" s="5"/>
+      <c r="E562" s="7"/>
     </row>
     <row r="563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E563" s="5"/>
+      <c r="E563" s="7"/>
     </row>
     <row r="564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E564" s="5"/>
+      <c r="E564" s="7"/>
     </row>
     <row r="565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E565" s="5"/>
+      <c r="E565" s="7"/>
     </row>
     <row r="566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E566" s="5"/>
+      <c r="E566" s="7"/>
     </row>
     <row r="567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E567" s="5"/>
+      <c r="E567" s="7"/>
     </row>
     <row r="568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E568" s="5"/>
+      <c r="E568" s="7"/>
     </row>
     <row r="569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E569" s="5"/>
+      <c r="E569" s="7"/>
     </row>
     <row r="570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E570" s="5"/>
+      <c r="E570" s="7"/>
     </row>
     <row r="571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E571" s="5"/>
+      <c r="E571" s="7"/>
     </row>
     <row r="572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E572" s="5"/>
+      <c r="E572" s="7"/>
     </row>
     <row r="573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E573" s="5"/>
+      <c r="E573" s="7"/>
     </row>
     <row r="574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E574" s="5"/>
+      <c r="E574" s="7"/>
     </row>
     <row r="575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E575" s="5"/>
+      <c r="E575" s="7"/>
     </row>
     <row r="576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E576" s="5"/>
+      <c r="E576" s="7"/>
     </row>
     <row r="577" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E577" s="5"/>
+      <c r="E577" s="7"/>
     </row>
     <row r="578" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E578" s="5"/>
+      <c r="E578" s="7"/>
     </row>
     <row r="579" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E579" s="5"/>
+      <c r="E579" s="7"/>
     </row>
     <row r="580" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E580" s="5"/>
+      <c r="E580" s="7"/>
     </row>
     <row r="581" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E581" s="5"/>
+      <c r="E581" s="7"/>
     </row>
     <row r="582" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E582" s="5"/>
+      <c r="E582" s="7"/>
     </row>
     <row r="583" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E583" s="5"/>
+      <c r="E583" s="7"/>
     </row>
     <row r="584" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E584" s="5"/>
+      <c r="E584" s="7"/>
     </row>
     <row r="585" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E585" s="5"/>
+      <c r="E585" s="7"/>
     </row>
     <row r="586" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E586" s="5"/>
+      <c r="E586" s="7"/>
     </row>
     <row r="587" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E587" s="5"/>
+      <c r="E587" s="7"/>
     </row>
     <row r="588" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E588" s="5"/>
+      <c r="E588" s="7"/>
     </row>
     <row r="589" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E589" s="5"/>
+      <c r="E589" s="7"/>
     </row>
     <row r="590" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E590" s="5"/>
+      <c r="E590" s="7"/>
     </row>
     <row r="591" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E591" s="5"/>
+      <c r="E591" s="7"/>
     </row>
     <row r="592" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E592" s="5"/>
+      <c r="E592" s="7"/>
     </row>
     <row r="593" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E593" s="5"/>
+      <c r="E593" s="7"/>
     </row>
     <row r="594" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E594" s="5"/>
+      <c r="E594" s="7"/>
     </row>
     <row r="595" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E595" s="5"/>
+      <c r="E595" s="7"/>
     </row>
     <row r="596" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E596" s="5"/>
+      <c r="E596" s="7"/>
     </row>
     <row r="597" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E597" s="5"/>
+      <c r="E597" s="7"/>
     </row>
     <row r="598" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E598" s="5"/>
+      <c r="E598" s="7"/>
     </row>
     <row r="599" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E599" s="5"/>
+      <c r="E599" s="7"/>
     </row>
     <row r="600" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E600" s="5"/>
+      <c r="E600" s="7"/>
     </row>
     <row r="601" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E601" s="5"/>
+      <c r="E601" s="7"/>
     </row>
     <row r="602" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E602" s="5"/>
+      <c r="E602" s="7"/>
     </row>
     <row r="603" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E603" s="5"/>
+      <c r="E603" s="7"/>
     </row>
     <row r="604" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E604" s="5"/>
+      <c r="E604" s="7"/>
     </row>
     <row r="605" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E605" s="5"/>
+      <c r="E605" s="7"/>
     </row>
     <row r="606" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E606" s="5"/>
+      <c r="E606" s="7"/>
     </row>
     <row r="607" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E607" s="5"/>
+      <c r="E607" s="7"/>
     </row>
     <row r="608" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E608" s="5"/>
+      <c r="E608" s="7"/>
     </row>
     <row r="609" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E609" s="5"/>
+      <c r="E609" s="7"/>
     </row>
     <row r="610" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E610" s="5"/>
+      <c r="E610" s="7"/>
     </row>
     <row r="611" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E611" s="5"/>
+      <c r="E611" s="7"/>
     </row>
     <row r="612" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E612" s="5"/>
+      <c r="E612" s="7"/>
     </row>
     <row r="613" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E613" s="5"/>
+      <c r="E613" s="7"/>
     </row>
     <row r="614" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E614" s="5"/>
+      <c r="E614" s="7"/>
     </row>
     <row r="615" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E615" s="5"/>
+      <c r="E615" s="7"/>
     </row>
     <row r="616" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E616" s="5"/>
+      <c r="E616" s="7"/>
     </row>
     <row r="617" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E617" s="5"/>
+      <c r="E617" s="7"/>
     </row>
     <row r="618" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E618" s="5"/>
+      <c r="E618" s="7"/>
     </row>
     <row r="619" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E619" s="5"/>
+      <c r="E619" s="7"/>
     </row>
     <row r="620" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E620" s="5"/>
+      <c r="E620" s="7"/>
     </row>
     <row r="621" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E621" s="5"/>
+      <c r="E621" s="7"/>
     </row>
     <row r="622" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E622" s="5"/>
+      <c r="E622" s="7"/>
     </row>
     <row r="623" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E623" s="5"/>
+      <c r="E623" s="7"/>
     </row>
     <row r="624" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E624" s="5"/>
+      <c r="E624" s="7"/>
     </row>
     <row r="625" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E625" s="5"/>
+      <c r="E625" s="7"/>
     </row>
     <row r="626" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E626" s="5"/>
+      <c r="E626" s="7"/>
     </row>
     <row r="627" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E627" s="5"/>
+      <c r="E627" s="7"/>
     </row>
     <row r="628" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E628" s="5"/>
+      <c r="E628" s="7"/>
     </row>
     <row r="629" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E629" s="5"/>
+      <c r="E629" s="7"/>
     </row>
     <row r="630" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E630" s="5"/>
+      <c r="E630" s="7"/>
     </row>
     <row r="631" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E631" s="5"/>
+      <c r="E631" s="7"/>
     </row>
     <row r="632" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E632" s="5"/>
+      <c r="E632" s="7"/>
     </row>
     <row r="633" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E633" s="5"/>
+      <c r="E633" s="7"/>
     </row>
     <row r="634" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E634" s="5"/>
+      <c r="E634" s="7"/>
     </row>
     <row r="635" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E635" s="5"/>
+      <c r="E635" s="7"/>
     </row>
     <row r="636" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E636" s="5"/>
+      <c r="E636" s="7"/>
     </row>
     <row r="637" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E637" s="5"/>
+      <c r="E637" s="7"/>
     </row>
     <row r="638" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E638" s="5"/>
+      <c r="E638" s="7"/>
     </row>
     <row r="639" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E639" s="5"/>
+      <c r="E639" s="7"/>
     </row>
     <row r="640" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E640" s="5"/>
+      <c r="E640" s="7"/>
     </row>
     <row r="641" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E641" s="5"/>
+      <c r="E641" s="7"/>
     </row>
     <row r="642" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E642" s="5"/>
+      <c r="E642" s="7"/>
     </row>
     <row r="643" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E643" s="5"/>
+      <c r="E643" s="7"/>
     </row>
     <row r="644" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E644" s="5"/>
+      <c r="E644" s="7"/>
     </row>
     <row r="645" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E645" s="5"/>
+      <c r="E645" s="7"/>
     </row>
     <row r="646" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E646" s="5"/>
+      <c r="E646" s="7"/>
     </row>
     <row r="647" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E647" s="5"/>
+      <c r="E647" s="7"/>
     </row>
     <row r="648" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E648" s="5"/>
+      <c r="E648" s="7"/>
     </row>
     <row r="649" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E649" s="5"/>
+      <c r="E649" s="7"/>
     </row>
     <row r="650" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E650" s="5"/>
+      <c r="E650" s="7"/>
     </row>
     <row r="651" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E651" s="5"/>
+      <c r="E651" s="7"/>
     </row>
     <row r="652" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E652" s="5"/>
+      <c r="E652" s="7"/>
     </row>
     <row r="653" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E653" s="5"/>
+      <c r="E653" s="7"/>
     </row>
     <row r="654" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E654" s="5"/>
+      <c r="E654" s="7"/>
     </row>
     <row r="655" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E655" s="5"/>
+      <c r="E655" s="7"/>
     </row>
     <row r="656" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E656" s="5"/>
+      <c r="E656" s="7"/>
     </row>
     <row r="657" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E657" s="5"/>
+      <c r="E657" s="7"/>
     </row>
     <row r="658" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E658" s="5"/>
+      <c r="E658" s="7"/>
     </row>
     <row r="659" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E659" s="5"/>
+      <c r="E659" s="7"/>
     </row>
     <row r="660" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E660" s="5"/>
+      <c r="E660" s="7"/>
     </row>
     <row r="661" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E661" s="5"/>
+      <c r="E661" s="7"/>
     </row>
     <row r="662" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E662" s="5"/>
+      <c r="E662" s="7"/>
     </row>
     <row r="663" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E663" s="5"/>
+      <c r="E663" s="7"/>
     </row>
     <row r="664" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E664" s="5"/>
+      <c r="E664" s="7"/>
     </row>
     <row r="665" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E665" s="5"/>
+      <c r="E665" s="7"/>
     </row>
     <row r="666" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E666" s="5"/>
+      <c r="E666" s="7"/>
     </row>
     <row r="667" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E667" s="5"/>
+      <c r="E667" s="7"/>
     </row>
     <row r="668" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E668" s="5"/>
+      <c r="E668" s="7"/>
     </row>
     <row r="669" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E669" s="5"/>
+      <c r="E669" s="7"/>
     </row>
     <row r="670" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E670" s="5"/>
+      <c r="E670" s="7"/>
     </row>
     <row r="671" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E671" s="5"/>
+      <c r="E671" s="7"/>
     </row>
     <row r="672" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E672" s="5"/>
+      <c r="E672" s="7"/>
     </row>
     <row r="673" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E673" s="5"/>
+      <c r="E673" s="7"/>
     </row>
     <row r="674" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E674" s="5"/>
+      <c r="E674" s="7"/>
     </row>
     <row r="675" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E675" s="5"/>
+      <c r="E675" s="7"/>
     </row>
     <row r="676" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E676" s="5"/>
+      <c r="E676" s="7"/>
     </row>
     <row r="677" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E677" s="5"/>
+      <c r="E677" s="7"/>
     </row>
     <row r="678" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E678" s="5"/>
+      <c r="E678" s="7"/>
     </row>
     <row r="679" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E679" s="5"/>
+      <c r="E679" s="7"/>
     </row>
     <row r="680" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E680" s="5"/>
+      <c r="E680" s="7"/>
     </row>
     <row r="681" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E681" s="5"/>
+      <c r="E681" s="7"/>
     </row>
     <row r="682" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E682" s="5"/>
+      <c r="E682" s="7"/>
     </row>
     <row r="683" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E683" s="5"/>
+      <c r="E683" s="7"/>
     </row>
     <row r="684" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E684" s="5"/>
+      <c r="E684" s="7"/>
     </row>
     <row r="685" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E685" s="5"/>
+      <c r="E685" s="7"/>
     </row>
     <row r="686" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E686" s="5"/>
+      <c r="E686" s="7"/>
     </row>
     <row r="687" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E687" s="5"/>
+      <c r="E687" s="7"/>
     </row>
     <row r="688" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E688" s="5"/>
+      <c r="E688" s="7"/>
     </row>
     <row r="689" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E689" s="5"/>
+      <c r="E689" s="7"/>
     </row>
     <row r="690" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E690" s="5"/>
+      <c r="E690" s="7"/>
     </row>
     <row r="691" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E691" s="5"/>
+      <c r="E691" s="7"/>
     </row>
     <row r="692" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E692" s="5"/>
+      <c r="E692" s="7"/>
     </row>
     <row r="693" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E693" s="5"/>
+      <c r="E693" s="7"/>
     </row>
     <row r="694" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E694" s="5"/>
+      <c r="E694" s="7"/>
     </row>
     <row r="695" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E695" s="5"/>
+      <c r="E695" s="7"/>
     </row>
     <row r="696" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E696" s="5"/>
+      <c r="E696" s="7"/>
     </row>
     <row r="697" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E697" s="5"/>
+      <c r="E697" s="7"/>
     </row>
     <row r="698" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E698" s="5"/>
+      <c r="E698" s="7"/>
     </row>
     <row r="699" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E699" s="5"/>
+      <c r="E699" s="7"/>
     </row>
     <row r="700" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E700" s="5"/>
+      <c r="E700" s="7"/>
     </row>
     <row r="701" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E701" s="5"/>
+      <c r="E701" s="7"/>
     </row>
     <row r="702" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E702" s="5"/>
+      <c r="E702" s="7"/>
     </row>
     <row r="703" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E703" s="5"/>
+      <c r="E703" s="7"/>
     </row>
     <row r="704" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E704" s="5"/>
+      <c r="E704" s="7"/>
     </row>
     <row r="705" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E705" s="5"/>
+      <c r="E705" s="7"/>
     </row>
     <row r="706" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E706" s="5"/>
+      <c r="E706" s="7"/>
     </row>
     <row r="707" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E707" s="5"/>
+      <c r="E707" s="7"/>
     </row>
     <row r="708" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E708" s="5"/>
+      <c r="E708" s="7"/>
     </row>
     <row r="709" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E709" s="5"/>
+      <c r="E709" s="7"/>
     </row>
     <row r="710" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E710" s="5"/>
+      <c r="E710" s="7"/>
     </row>
     <row r="711" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E711" s="5"/>
+      <c r="E711" s="7"/>
     </row>
     <row r="712" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E712" s="5"/>
+      <c r="E712" s="7"/>
     </row>
     <row r="713" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E713" s="5"/>
+      <c r="E713" s="7"/>
     </row>
     <row r="714" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E714" s="5"/>
+      <c r="E714" s="7"/>
     </row>
     <row r="715" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E715" s="5"/>
+      <c r="E715" s="7"/>
     </row>
     <row r="716" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E716" s="5"/>
+      <c r="E716" s="7"/>
     </row>
     <row r="717" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E717" s="5"/>
+      <c r="E717" s="7"/>
     </row>
     <row r="718" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E718" s="5"/>
+      <c r="E718" s="7"/>
     </row>
     <row r="719" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E719" s="5"/>
+      <c r="E719" s="7"/>
     </row>
     <row r="720" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E720" s="5"/>
+      <c r="E720" s="7"/>
     </row>
     <row r="721" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E721" s="5"/>
+      <c r="E721" s="7"/>
     </row>
     <row r="722" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E722" s="5"/>
+      <c r="E722" s="7"/>
     </row>
     <row r="723" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E723" s="5"/>
+      <c r="E723" s="7"/>
     </row>
     <row r="724" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E724" s="5"/>
+      <c r="E724" s="7"/>
     </row>
     <row r="725" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E725" s="5"/>
+      <c r="E725" s="7"/>
     </row>
     <row r="726" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E726" s="5"/>
+      <c r="E726" s="7"/>
     </row>
     <row r="727" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E727" s="5"/>
+      <c r="E727" s="7"/>
     </row>
     <row r="728" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E728" s="5"/>
+      <c r="E728" s="7"/>
     </row>
     <row r="729" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E729" s="5"/>
+      <c r="E729" s="7"/>
     </row>
     <row r="730" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E730" s="5"/>
+      <c r="E730" s="7"/>
     </row>
     <row r="731" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E731" s="5"/>
+      <c r="E731" s="7"/>
     </row>
     <row r="732" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E732" s="5"/>
+      <c r="E732" s="7"/>
     </row>
     <row r="733" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E733" s="5"/>
+      <c r="E733" s="7"/>
     </row>
     <row r="734" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E734" s="5"/>
+      <c r="E734" s="7"/>
     </row>
     <row r="735" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E735" s="5"/>
+      <c r="E735" s="7"/>
     </row>
     <row r="736" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E736" s="5"/>
+      <c r="E736" s="7"/>
     </row>
     <row r="737" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E737" s="5"/>
+      <c r="E737" s="7"/>
     </row>
     <row r="738" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E738" s="5"/>
+      <c r="E738" s="7"/>
     </row>
     <row r="739" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E739" s="5"/>
+      <c r="E739" s="7"/>
     </row>
     <row r="740" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E740" s="5"/>
+      <c r="E740" s="7"/>
     </row>
     <row r="741" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E741" s="5"/>
+      <c r="E741" s="7"/>
     </row>
     <row r="742" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E742" s="5"/>
+      <c r="E742" s="7"/>
     </row>
     <row r="743" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E743" s="5"/>
+      <c r="E743" s="7"/>
     </row>
     <row r="744" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E744" s="5"/>
+      <c r="E744" s="7"/>
     </row>
     <row r="745" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E745" s="5"/>
+      <c r="E745" s="7"/>
     </row>
     <row r="746" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E746" s="5"/>
+      <c r="E746" s="7"/>
     </row>
     <row r="747" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E747" s="5"/>
+      <c r="E747" s="7"/>
     </row>
     <row r="748" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E748" s="5"/>
+      <c r="E748" s="7"/>
     </row>
     <row r="749" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E749" s="5"/>
+      <c r="E749" s="7"/>
     </row>
     <row r="750" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E750" s="5"/>
+      <c r="E750" s="7"/>
     </row>
     <row r="751" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E751" s="5"/>
+      <c r="E751" s="7"/>
     </row>
     <row r="752" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E752" s="5"/>
+      <c r="E752" s="7"/>
     </row>
     <row r="753" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E753" s="5"/>
+      <c r="E753" s="7"/>
     </row>
     <row r="754" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E754" s="5"/>
+      <c r="E754" s="7"/>
     </row>
     <row r="755" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E755" s="5"/>
+      <c r="E755" s="7"/>
     </row>
     <row r="756" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E756" s="5"/>
+      <c r="E756" s="7"/>
     </row>
     <row r="757" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E757" s="5"/>
+      <c r="E757" s="7"/>
     </row>
     <row r="758" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E758" s="5"/>
+      <c r="E758" s="7"/>
     </row>
     <row r="759" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E759" s="5"/>
+      <c r="E759" s="7"/>
     </row>
     <row r="760" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E760" s="5"/>
+      <c r="E760" s="7"/>
     </row>
     <row r="761" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E761" s="5"/>
+      <c r="E761" s="7"/>
     </row>
     <row r="762" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E762" s="5"/>
+      <c r="E762" s="7"/>
     </row>
     <row r="763" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E763" s="5"/>
+      <c r="E763" s="7"/>
     </row>
     <row r="764" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E764" s="5"/>
+      <c r="E764" s="7"/>
     </row>
     <row r="765" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E765" s="5"/>
+      <c r="E765" s="7"/>
     </row>
     <row r="766" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E766" s="5"/>
+      <c r="E766" s="7"/>
     </row>
     <row r="767" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E767" s="5"/>
+      <c r="E767" s="7"/>
     </row>
     <row r="768" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E768" s="5"/>
+      <c r="E768" s="7"/>
     </row>
     <row r="769" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E769" s="5"/>
+      <c r="E769" s="7"/>
     </row>
     <row r="770" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E770" s="5"/>
+      <c r="E770" s="7"/>
     </row>
     <row r="771" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E771" s="5"/>
+      <c r="E771" s="7"/>
     </row>
     <row r="772" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E772" s="5"/>
+      <c r="E772" s="7"/>
     </row>
     <row r="773" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E773" s="5"/>
+      <c r="E773" s="7"/>
     </row>
     <row r="774" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E774" s="5"/>
+      <c r="E774" s="7"/>
     </row>
     <row r="775" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E775" s="5"/>
+      <c r="E775" s="7"/>
     </row>
     <row r="776" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E776" s="5"/>
+      <c r="E776" s="7"/>
     </row>
     <row r="777" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E777" s="5"/>
+      <c r="E777" s="7"/>
     </row>
     <row r="778" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E778" s="5"/>
+      <c r="E778" s="7"/>
     </row>
     <row r="779" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E779" s="5"/>
+      <c r="E779" s="7"/>
     </row>
     <row r="780" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E780" s="5"/>
+      <c r="E780" s="7"/>
     </row>
     <row r="781" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E781" s="5"/>
+      <c r="E781" s="7"/>
     </row>
     <row r="782" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E782" s="5"/>
+      <c r="E782" s="7"/>
     </row>
     <row r="783" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E783" s="5"/>
+      <c r="E783" s="7"/>
     </row>
     <row r="784" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E784" s="5"/>
+      <c r="E784" s="7"/>
     </row>
     <row r="785" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E785" s="5"/>
+      <c r="E785" s="7"/>
     </row>
     <row r="786" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E786" s="5"/>
+      <c r="E786" s="7"/>
     </row>
     <row r="787" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E787" s="5"/>
+      <c r="E787" s="7"/>
     </row>
     <row r="788" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E788" s="5"/>
+      <c r="E788" s="7"/>
     </row>
     <row r="789" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E789" s="5"/>
+      <c r="E789" s="7"/>
     </row>
     <row r="790" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E790" s="5"/>
+      <c r="E790" s="7"/>
     </row>
     <row r="791" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E791" s="5"/>
+      <c r="E791" s="7"/>
     </row>
     <row r="792" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E792" s="5"/>
+      <c r="E792" s="7"/>
     </row>
     <row r="793" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E793" s="5"/>
+      <c r="E793" s="7"/>
     </row>
     <row r="794" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E794" s="5"/>
+      <c r="E794" s="7"/>
     </row>
     <row r="795" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E795" s="5"/>
+      <c r="E795" s="7"/>
     </row>
     <row r="796" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E796" s="5"/>
+      <c r="E796" s="7"/>
     </row>
     <row r="797" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E797" s="5"/>
+      <c r="E797" s="7"/>
     </row>
     <row r="798" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E798" s="5"/>
+      <c r="E798" s="7"/>
     </row>
     <row r="799" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E799" s="5"/>
+      <c r="E799" s="7"/>
     </row>
     <row r="800" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E800" s="5"/>
+      <c r="E800" s="7"/>
     </row>
     <row r="801" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E801" s="5"/>
+      <c r="E801" s="7"/>
     </row>
     <row r="802" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E802" s="5"/>
+      <c r="E802" s="7"/>
     </row>
     <row r="803" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E803" s="5"/>
+      <c r="E803" s="7"/>
     </row>
     <row r="804" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E804" s="5"/>
+      <c r="E804" s="7"/>
     </row>
     <row r="805" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E805" s="5"/>
+      <c r="E805" s="7"/>
     </row>
     <row r="806" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E806" s="5"/>
+      <c r="E806" s="7"/>
     </row>
     <row r="807" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E807" s="5"/>
+      <c r="E807" s="7"/>
     </row>
     <row r="808" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E808" s="5"/>
+      <c r="E808" s="7"/>
     </row>
     <row r="809" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E809" s="5"/>
+      <c r="E809" s="7"/>
     </row>
     <row r="810" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E810" s="5"/>
+      <c r="E810" s="7"/>
     </row>
     <row r="811" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E811" s="5"/>
+      <c r="E811" s="7"/>
     </row>
     <row r="812" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E812" s="5"/>
+      <c r="E812" s="7"/>
     </row>
     <row r="813" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E813" s="5"/>
+      <c r="E813" s="7"/>
     </row>
     <row r="814" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E814" s="5"/>
+      <c r="E814" s="7"/>
     </row>
     <row r="815" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E815" s="5"/>
+      <c r="E815" s="7"/>
     </row>
     <row r="816" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E816" s="5"/>
+      <c r="E816" s="7"/>
     </row>
     <row r="817" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E817" s="5"/>
+      <c r="E817" s="7"/>
     </row>
     <row r="818" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E818" s="5"/>
+      <c r="E818" s="7"/>
     </row>
     <row r="819" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E819" s="5"/>
+      <c r="E819" s="7"/>
     </row>
     <row r="820" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E820" s="5"/>
+      <c r="E820" s="7"/>
     </row>
     <row r="821" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E821" s="5"/>
+      <c r="E821" s="7"/>
     </row>
     <row r="822" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E822" s="5"/>
+      <c r="E822" s="7"/>
     </row>
     <row r="823" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E823" s="5"/>
+      <c r="E823" s="7"/>
     </row>
     <row r="824" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E824" s="5"/>
+      <c r="E824" s="7"/>
     </row>
     <row r="825" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E825" s="5"/>
+      <c r="E825" s="7"/>
     </row>
     <row r="826" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E826" s="5"/>
+      <c r="E826" s="7"/>
     </row>
     <row r="827" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E827" s="5"/>
+      <c r="E827" s="7"/>
     </row>
     <row r="828" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E828" s="5"/>
+      <c r="E828" s="7"/>
     </row>
     <row r="829" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E829" s="5"/>
+      <c r="E829" s="7"/>
     </row>
     <row r="830" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E830" s="5"/>
+      <c r="E830" s="7"/>
     </row>
     <row r="831" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E831" s="5"/>
+      <c r="E831" s="7"/>
     </row>
     <row r="832" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E832" s="5"/>
+      <c r="E832" s="7"/>
     </row>
     <row r="833" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E833" s="5"/>
+      <c r="E833" s="7"/>
     </row>
     <row r="834" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E834" s="5"/>
+      <c r="E834" s="7"/>
     </row>
     <row r="835" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E835" s="5"/>
+      <c r="E835" s="7"/>
     </row>
     <row r="836" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E836" s="5"/>
+      <c r="E836" s="7"/>
     </row>
     <row r="837" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E837" s="5"/>
+      <c r="E837" s="7"/>
     </row>
     <row r="838" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E838" s="5"/>
+      <c r="E838" s="7"/>
     </row>
     <row r="839" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E839" s="5"/>
+      <c r="E839" s="7"/>
     </row>
     <row r="840" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E840" s="5"/>
+      <c r="E840" s="7"/>
     </row>
     <row r="841" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E841" s="5"/>
+      <c r="E841" s="7"/>
     </row>
     <row r="842" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E842" s="5"/>
+      <c r="E842" s="7"/>
     </row>
     <row r="843" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E843" s="5"/>
+      <c r="E843" s="7"/>
     </row>
     <row r="844" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E844" s="5"/>
+      <c r="E844" s="7"/>
     </row>
     <row r="845" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E845" s="5"/>
+      <c r="E845" s="7"/>
     </row>
     <row r="846" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E846" s="5"/>
+      <c r="E846" s="7"/>
     </row>
     <row r="847" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E847" s="5"/>
+      <c r="E847" s="7"/>
     </row>
     <row r="848" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E848" s="5"/>
+      <c r="E848" s="7"/>
     </row>
     <row r="849" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E849" s="5"/>
+      <c r="E849" s="7"/>
     </row>
     <row r="850" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E850" s="5"/>
+      <c r="E850" s="7"/>
     </row>
     <row r="851" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E851" s="5"/>
+      <c r="E851" s="7"/>
     </row>
     <row r="852" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E852" s="5"/>
+      <c r="E852" s="7"/>
     </row>
     <row r="853" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E853" s="5"/>
+      <c r="E853" s="7"/>
     </row>
     <row r="854" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E854" s="5"/>
+      <c r="E854" s="7"/>
     </row>
     <row r="855" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E855" s="5"/>
+      <c r="E855" s="7"/>
     </row>
     <row r="856" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E856" s="5"/>
+      <c r="E856" s="7"/>
     </row>
     <row r="857" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E857" s="5"/>
+      <c r="E857" s="7"/>
     </row>
     <row r="858" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E858" s="5"/>
+      <c r="E858" s="7"/>
     </row>
     <row r="859" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E859" s="5"/>
+      <c r="E859" s="7"/>
     </row>
     <row r="860" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E860" s="5"/>
+      <c r="E860" s="7"/>
     </row>
     <row r="861" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E861" s="5"/>
+      <c r="E861" s="7"/>
     </row>
     <row r="862" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E862" s="5"/>
+      <c r="E862" s="7"/>
     </row>
     <row r="863" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E863" s="5"/>
+      <c r="E863" s="7"/>
     </row>
     <row r="864" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E864" s="5"/>
+      <c r="E864" s="7"/>
     </row>
     <row r="865" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E865" s="5"/>
+      <c r="E865" s="7"/>
     </row>
     <row r="866" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E866" s="5"/>
+      <c r="E866" s="7"/>
     </row>
     <row r="867" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E867" s="5"/>
+      <c r="E867" s="7"/>
     </row>
     <row r="868" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E868" s="5"/>
+      <c r="E868" s="7"/>
     </row>
     <row r="869" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E869" s="5"/>
+      <c r="E869" s="7"/>
     </row>
     <row r="870" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E870" s="5"/>
+      <c r="E870" s="7"/>
     </row>
     <row r="871" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E871" s="5"/>
+      <c r="E871" s="7"/>
     </row>
     <row r="872" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E872" s="5"/>
+      <c r="E872" s="7"/>
     </row>
     <row r="873" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E873" s="5"/>
+      <c r="E873" s="7"/>
     </row>
     <row r="874" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E874" s="5"/>
+      <c r="E874" s="7"/>
     </row>
     <row r="875" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E875" s="5"/>
+      <c r="E875" s="7"/>
     </row>
     <row r="876" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E876" s="5"/>
+      <c r="E876" s="7"/>
     </row>
     <row r="877" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E877" s="5"/>
+      <c r="E877" s="7"/>
     </row>
     <row r="878" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E878" s="5"/>
+      <c r="E878" s="7"/>
     </row>
     <row r="879" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E879" s="5"/>
+      <c r="E879" s="7"/>
     </row>
     <row r="880" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E880" s="5"/>
+      <c r="E880" s="7"/>
     </row>
     <row r="881" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E881" s="5"/>
+      <c r="E881" s="7"/>
     </row>
     <row r="882" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E882" s="5"/>
+      <c r="E882" s="7"/>
     </row>
     <row r="883" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E883" s="5"/>
+      <c r="E883" s="7"/>
     </row>
     <row r="884" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E884" s="5"/>
+      <c r="E884" s="7"/>
     </row>
     <row r="885" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E885" s="5"/>
+      <c r="E885" s="7"/>
     </row>
     <row r="886" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E886" s="5"/>
+      <c r="E886" s="7"/>
     </row>
     <row r="887" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E887" s="5"/>
+      <c r="E887" s="7"/>
     </row>
     <row r="888" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E888" s="5"/>
+      <c r="E888" s="7"/>
     </row>
     <row r="889" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E889" s="5"/>
+      <c r="E889" s="7"/>
     </row>
     <row r="890" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E890" s="5"/>
+      <c r="E890" s="7"/>
     </row>
     <row r="891" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E891" s="5"/>
+      <c r="E891" s="7"/>
     </row>
     <row r="892" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E892" s="5"/>
+      <c r="E892" s="7"/>
     </row>
     <row r="893" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E893" s="5"/>
+      <c r="E893" s="7"/>
     </row>
     <row r="894" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E894" s="5"/>
+      <c r="E894" s="7"/>
     </row>
     <row r="895" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E895" s="5"/>
+      <c r="E895" s="7"/>
     </row>
     <row r="896" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E896" s="5"/>
+      <c r="E896" s="7"/>
     </row>
     <row r="897" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E897" s="5"/>
+      <c r="E897" s="7"/>
     </row>
     <row r="898" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E898" s="5"/>
+      <c r="E898" s="7"/>
     </row>
     <row r="899" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E899" s="5"/>
+      <c r="E899" s="7"/>
     </row>
     <row r="900" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E900" s="5"/>
+      <c r="E900" s="7"/>
     </row>
     <row r="901" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E901" s="5"/>
+      <c r="E901" s="7"/>
     </row>
     <row r="902" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E902" s="5"/>
+      <c r="E902" s="7"/>
     </row>
     <row r="903" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E903" s="5"/>
+      <c r="E903" s="7"/>
     </row>
     <row r="904" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E904" s="5"/>
+      <c r="E904" s="7"/>
     </row>
     <row r="905" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E905" s="5"/>
+      <c r="E905" s="7"/>
     </row>
     <row r="906" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E906" s="5"/>
+      <c r="E906" s="7"/>
     </row>
     <row r="907" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E907" s="5"/>
+      <c r="E907" s="7"/>
     </row>
     <row r="908" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E908" s="5"/>
+      <c r="E908" s="7"/>
     </row>
     <row r="909" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E909" s="5"/>
+      <c r="E909" s="7"/>
     </row>
     <row r="910" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E910" s="5"/>
+      <c r="E910" s="7"/>
     </row>
     <row r="911" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E911" s="5"/>
+      <c r="E911" s="7"/>
     </row>
     <row r="912" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E912" s="5"/>
+      <c r="E912" s="7"/>
     </row>
     <row r="913" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E913" s="5"/>
+      <c r="E913" s="7"/>
     </row>
     <row r="914" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E914" s="5"/>
+      <c r="E914" s="7"/>
     </row>
     <row r="915" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E915" s="5"/>
+      <c r="E915" s="7"/>
     </row>
     <row r="916" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E916" s="5"/>
+      <c r="E916" s="7"/>
     </row>
     <row r="917" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E917" s="5"/>
+      <c r="E917" s="7"/>
     </row>
     <row r="918" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E918" s="5"/>
+      <c r="E918" s="7"/>
     </row>
     <row r="919" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E919" s="5"/>
+      <c r="E919" s="7"/>
     </row>
     <row r="920" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E920" s="5"/>
+      <c r="E920" s="7"/>
     </row>
     <row r="921" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E921" s="5"/>
+      <c r="E921" s="7"/>
     </row>
     <row r="922" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E922" s="5"/>
+      <c r="E922" s="7"/>
     </row>
     <row r="923" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E923" s="5"/>
+      <c r="E923" s="7"/>
     </row>
     <row r="924" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E924" s="5"/>
+      <c r="E924" s="7"/>
     </row>
     <row r="925" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E925" s="5"/>
+      <c r="E925" s="7"/>
     </row>
     <row r="926" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E926" s="5"/>
+      <c r="E926" s="7"/>
     </row>
     <row r="927" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E927" s="5"/>
+      <c r="E927" s="7"/>
     </row>
     <row r="928" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E928" s="5"/>
+      <c r="E928" s="7"/>
     </row>
     <row r="929" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E929" s="5"/>
+      <c r="E929" s="7"/>
     </row>
     <row r="930" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E930" s="5"/>
+      <c r="E930" s="7"/>
     </row>
     <row r="931" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E931" s="5"/>
+      <c r="E931" s="7"/>
     </row>
     <row r="932" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E932" s="5"/>
+      <c r="E932" s="7"/>
     </row>
     <row r="933" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E933" s="5"/>
+      <c r="E933" s="7"/>
     </row>
     <row r="934" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E934" s="5"/>
+      <c r="E934" s="7"/>
     </row>
     <row r="935" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E935" s="5"/>
+      <c r="E935" s="7"/>
     </row>
     <row r="936" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E936" s="5"/>
+      <c r="E936" s="7"/>
     </row>
     <row r="937" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E937" s="5"/>
+      <c r="E937" s="7"/>
     </row>
     <row r="938" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E938" s="5"/>
+      <c r="E938" s="7"/>
     </row>
     <row r="939" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E939" s="5"/>
+      <c r="E939" s="7"/>
     </row>
     <row r="940" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E940" s="5"/>
+      <c r="E940" s="7"/>
     </row>
     <row r="941" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E941" s="5"/>
+      <c r="E941" s="7"/>
     </row>
     <row r="942" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E942" s="5"/>
+      <c r="E942" s="7"/>
     </row>
     <row r="943" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E943" s="5"/>
+      <c r="E943" s="7"/>
     </row>
     <row r="944" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E944" s="5"/>
+      <c r="E944" s="7"/>
     </row>
     <row r="945" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E945" s="5"/>
+      <c r="E945" s="7"/>
     </row>
     <row r="946" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E946" s="5"/>
+      <c r="E946" s="7"/>
     </row>
     <row r="947" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E947" s="5"/>
+      <c r="E947" s="7"/>
     </row>
     <row r="948" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E948" s="5"/>
+      <c r="E948" s="7"/>
     </row>
     <row r="949" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E949" s="5"/>
+      <c r="E949" s="7"/>
     </row>
     <row r="950" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E950" s="5"/>
+      <c r="E950" s="7"/>
     </row>
     <row r="951" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E951" s="5"/>
+      <c r="E951" s="7"/>
     </row>
     <row r="952" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E952" s="5"/>
+      <c r="E952" s="7"/>
     </row>
     <row r="953" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E953" s="5"/>
+      <c r="E953" s="7"/>
     </row>
     <row r="954" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E954" s="5"/>
+      <c r="E954" s="7"/>
     </row>
     <row r="955" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E955" s="5"/>
+      <c r="E955" s="7"/>
     </row>
     <row r="956" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E956" s="5"/>
+      <c r="E956" s="7"/>
     </row>
     <row r="957" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E957" s="5"/>
+      <c r="E957" s="7"/>
     </row>
     <row r="958" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E958" s="5"/>
+      <c r="E958" s="7"/>
     </row>
     <row r="959" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E959" s="5"/>
+      <c r="E959" s="7"/>
     </row>
     <row r="960" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E960" s="5"/>
+      <c r="E960" s="7"/>
     </row>
     <row r="961" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E961" s="5"/>
+      <c r="E961" s="7"/>
     </row>
     <row r="962" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E962" s="5"/>
+      <c r="E962" s="7"/>
     </row>
     <row r="963" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E963" s="5"/>
+      <c r="E963" s="7"/>
     </row>
     <row r="964" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E964" s="5"/>
+      <c r="E964" s="7"/>
     </row>
     <row r="965" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E965" s="5"/>
+      <c r="E965" s="7"/>
     </row>
     <row r="966" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E966" s="5"/>
+      <c r="E966" s="7"/>
     </row>
     <row r="967" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E967" s="5"/>
+      <c r="E967" s="7"/>
     </row>
     <row r="968" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E968" s="5"/>
+      <c r="E968" s="7"/>
     </row>
     <row r="969" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E969" s="5"/>
+      <c r="E969" s="7"/>
     </row>
     <row r="970" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E970" s="5"/>
+      <c r="E970" s="7"/>
     </row>
     <row r="971" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E971" s="5"/>
+      <c r="E971" s="7"/>
     </row>
     <row r="972" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E972" s="5"/>
+      <c r="E972" s="7"/>
     </row>
     <row r="973" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E973" s="5"/>
+      <c r="E973" s="7"/>
     </row>
     <row r="974" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E974" s="5"/>
+      <c r="E974" s="7"/>
     </row>
     <row r="975" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E975" s="5"/>
+      <c r="E975" s="7"/>
     </row>
     <row r="976" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E976" s="5"/>
+      <c r="E976" s="7"/>
     </row>
     <row r="977" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E977" s="5"/>
+      <c r="E977" s="7"/>
     </row>
     <row r="978" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E978" s="5"/>
+      <c r="E978" s="7"/>
     </row>
     <row r="979" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E979" s="5"/>
+      <c r="E979" s="7"/>
     </row>
     <row r="980" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E980" s="5"/>
+      <c r="E980" s="7"/>
     </row>
     <row r="981" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E981" s="5"/>
+      <c r="E981" s="7"/>
     </row>
     <row r="982" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E982" s="5"/>
+      <c r="E982" s="7"/>
     </row>
     <row r="983" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E983" s="5"/>
+      <c r="E983" s="7"/>
     </row>
     <row r="984" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E984" s="5"/>
+      <c r="E984" s="7"/>
     </row>
     <row r="985" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E985" s="5"/>
+      <c r="E985" s="7"/>
     </row>
     <row r="986" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E986" s="5"/>
+      <c r="E986" s="7"/>
     </row>
     <row r="987" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E987" s="5"/>
+      <c r="E987" s="7"/>
     </row>
     <row r="988" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E988" s="5"/>
+      <c r="E988" s="7"/>
     </row>
     <row r="989" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E989" s="5"/>
+      <c r="E989" s="7"/>
     </row>
     <row r="990" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E990" s="5"/>
+      <c r="E990" s="7"/>
     </row>
     <row r="991" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E991" s="5"/>
+      <c r="E991" s="7"/>
     </row>
     <row r="992" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E992" s="5"/>
+      <c r="E992" s="7"/>
     </row>
     <row r="993" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E993" s="5"/>
+      <c r="E993" s="7"/>
     </row>
     <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E994" s="5"/>
+      <c r="E994" s="7"/>
     </row>
     <row r="995" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E995" s="5"/>
+      <c r="E995" s="7"/>
     </row>
     <row r="996" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E996" s="5"/>
+      <c r="E996" s="7"/>
     </row>
     <row r="997" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E997" s="5"/>
+      <c r="E997" s="7"/>
     </row>
     <row r="998" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E998" s="5"/>
+      <c r="E998" s="7"/>
     </row>
     <row r="999" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E999" s="5"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="E999" s="7"/>
+    </row>
+    <row r="1000" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E1000" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E1:E99" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E1:E57 E59:E100" type="list">
       <formula1>"Antwort A,Antwort B,Gleichwertig"</formula1>
       <formula2>0</formula2>
     </dataValidation>
